--- a/web_app/temp/excel/hard_cases.xlsx
+++ b/web_app/temp/excel/hard_cases.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\資策會_AI新秀計畫_智慧系統實作班\專案\mma_jupyter\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MyData\TW_mobile\mix\money-api\web_app\temp\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2B4F611-2E6A-4FDA-A799-932544B576AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89D16EAE-1038-4A9D-8395-DCF56CB90F1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4395" yWindow="2715" windowWidth="22260" windowHeight="12765" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1170" yWindow="2340" windowWidth="10740" windowHeight="12765" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="51">
   <si>
     <t>text</t>
   </si>
@@ -111,6 +111,69 @@
   <si>
     <t>今天去打排球前前飛了400元請幫我記帳，到底要開心還難過?</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>我這個月覺得錢包好扁，是不是買東西變貴了？</t>
+  </si>
+  <si>
+    <t>這個月花費合理嗎？物價有變貴嗎？</t>
+  </si>
+  <si>
+    <t>我最近一直存不到錢，請幫我診斷消費是否正常？</t>
+  </si>
+  <si>
+    <t>我的消費狀況正不正常？</t>
+  </si>
+  <si>
+    <t>最近通膨很嚴重，我應該怎麼調整理財計畫？</t>
+  </si>
+  <si>
+    <t>感覺這個月花很多，你覺得我消費合理嗎？</t>
+  </si>
+  <si>
+    <t>我的薪水算高嗎？跟同行比起來如何？</t>
+  </si>
+  <si>
+    <t>幫我分析我的財務狀況是否健康？</t>
+  </si>
+  <si>
+    <t>這個月的消費占比正常嗎？</t>
+  </si>
+  <si>
+    <t>2026年4月物價有沒有變貴？</t>
+  </si>
+  <si>
+    <t>最近一直存不了錢，我的消費習慣有問題嗎？</t>
+  </si>
+  <si>
+    <t>請幫我做財務健康診斷</t>
+  </si>
+  <si>
+    <t>我覺得我花太多錢了，幫我檢視一下</t>
+  </si>
+  <si>
+    <t>任務系統怎麼用？</t>
+  </si>
+  <si>
+    <t>怎麼新增帳戶？</t>
+  </si>
+  <si>
+    <t>卡牌系統是什麼規則？</t>
+  </si>
+  <si>
+    <t>天氣好好喔，心情很好！</t>
+  </si>
+  <si>
+    <t>今天好累喔</t>
+  </si>
+  <si>
+    <t>這個月總支出是多少？</t>
+  </si>
+  <si>
+    <t>我的飲食類別花了多少錢？</t>
+  </si>
+  <si>
+    <t>上個月存了多少？</t>
   </si>
 </sst>
 </file>
@@ -457,7 +520,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:B43"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="63.42578125" customWidth="1"/>
@@ -641,6 +704,174 @@
         <v>9</v>
       </c>
     </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>30</v>
+      </c>
+      <c r="B23" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>31</v>
+      </c>
+      <c r="B24" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>32</v>
+      </c>
+      <c r="B25" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>33</v>
+      </c>
+      <c r="B26" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>34</v>
+      </c>
+      <c r="B27" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>35</v>
+      </c>
+      <c r="B28" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>36</v>
+      </c>
+      <c r="B29" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>37</v>
+      </c>
+      <c r="B30" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>38</v>
+      </c>
+      <c r="B31" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>39</v>
+      </c>
+      <c r="B32" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>40</v>
+      </c>
+      <c r="B33" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>41</v>
+      </c>
+      <c r="B34" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>42</v>
+      </c>
+      <c r="B35" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>43</v>
+      </c>
+      <c r="B36" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>44</v>
+      </c>
+      <c r="B37" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>45</v>
+      </c>
+      <c r="B38" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>46</v>
+      </c>
+      <c r="B39" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>47</v>
+      </c>
+      <c r="B40" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>48</v>
+      </c>
+      <c r="B41" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>49</v>
+      </c>
+      <c r="B42" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>50</v>
+      </c>
+      <c r="B43" t="s">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
